--- a/batch-2026-08.xlsx
+++ b/batch-2026-08.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新申請" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="測試說明" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="新申請" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="測試說明" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -604,6 +604,11 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>送出時間</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>預期結果</t>
         </is>
       </c>
@@ -642,6 +647,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>2026-08-05 09:00</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>通過</t>
         </is>
       </c>
@@ -680,6 +690,11 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>2026-08-05 10:00</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>通過</t>
         </is>
       </c>
@@ -718,6 +733,11 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>2026-08-05 11:00</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>通過</t>
         </is>
       </c>
@@ -755,6 +775,11 @@
         </is>
       </c>
       <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-08-05 12:00</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>通過</t>
         </is>
